--- a/data/trans_dic/P64D$otros_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,35</t>
+          <t>0,35; 3,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,91</t>
+          <t>0,23; 2,16</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,58</t>
+          <t>0,12; 1,83</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,18</t>
+          <t>0,38; 2,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,12</t>
+          <t>0,28; 2,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,65</t>
+          <t>0,49; 1,67</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,6</t>
+          <t>0,32; 4,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,16</t>
+          <t>0,31; 2,27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,41; 1,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,25; 1,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,45; 1,07</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,43; 1,34</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 1,17</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 1,07</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en otros medios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1266; 11740</t>
+          <t>1212; 11846</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 9003</t>
+          <t>0; 6249</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1672; 12684</t>
+          <t>1556; 14351</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4755</t>
+          <t>0; 4565</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7935</t>
+          <t>0; 9650</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>663; 8772</t>
+          <t>659; 10177</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8287</t>
+          <t>0; 8474</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1190</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7525</t>
+          <t>0; 7653</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2203; 12196</t>
+          <t>2141; 12300</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1157; 9034</t>
+          <t>1209; 9579</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4381; 16272</t>
+          <t>4819; 16424</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>941; 11030</t>
+          <t>758; 10593</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4901</t>
+          <t>0; 4580</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1717; 13243</t>
+          <t>1913; 13914</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24209</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7989; 26911</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3660; 15887</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15374; 36340</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>15738</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>8471</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>24209</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>8412; 26116</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3804; 16811</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>15481; 36176</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P64D$otros_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$otros_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,38</t>
+          <t>0,37; 3,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,16</t>
+          <t>0,37; 2,01</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,83</t>
+          <t>0,12; 1,59</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,2</t>
+          <t>0,58; 2,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,25</t>
+          <t>0,55; 3,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,67</t>
+          <t>0,8; 2,47</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,42</t>
+          <t>0,46; 3,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,23</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,27</t>
+          <t>0,37; 2,1</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,38</t>
+          <t>0,65; 1,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,1</t>
+          <t>0,42; 1,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,07</t>
+          <t>0,64; 1,35</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4095</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>6905</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1212; 11846</t>
+          <t>1416; 13515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6249</t>
+          <t>0; 7207</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1556; 14351</t>
+          <t>2674; 14349</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>866</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3017</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4565</t>
+          <t>0; 4984</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 9650</t>
+          <t>0; 8016</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>659; 10177</t>
+          <t>705; 9455</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1271</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 8474</t>
+          <t>0; 6821</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7653</t>
+          <t>0; 6415</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9001</t>
+          <t>15529</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2141; 12300</t>
+          <t>3613; 16578</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1209; 9579</t>
+          <t>2622; 16027</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4819; 16424</t>
+          <t>8745; 27189</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>5976</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>758; 10593</t>
+          <t>1408; 11680</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4580</t>
+          <t>0; 4133</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1913; 13914</t>
+          <t>2307; 13039</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>20449</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>12248</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>24209</t>
+          <t>32698</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7989; 26911</t>
+          <t>12268; 31738</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3660; 15887</t>
+          <t>6197; 21657</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15374; 36340</t>
+          <t>21677; 45769</t>
         </is>
       </c>
     </row>
